--- a/cleaning_pipeline_R/dictionaries/dictionary_zim_maternal_outcomes_enriched.xlsx
+++ b/cleaning_pipeline_R/dictionaries/dictionary_zim_maternal_outcomes_enriched.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="41">
   <si>
     <t xml:space="preserve">display_label</t>
   </si>
@@ -51,7 +51,7 @@
     <t xml:space="preserve">Mother''s Initials</t>
   </si>
   <si>
-    <t xml:space="preserve">Outcome</t>
+    <t xml:space="preserve">Outcome at discharge</t>
   </si>
   <si>
     <t xml:space="preserve">Did the baby require immediate resuscitation?</t>
@@ -88,6 +88,9 @@
   </si>
   <si>
     <t xml:space="preserve">Mode of delivery</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Outcome</t>
   </si>
   <si>
     <t xml:space="preserve">Was resuscitation given?</t>
@@ -607,25 +610,25 @@
         <v>19</v>
       </c>
       <c r="AB1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AC1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="AD1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="AE1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="AF1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="AG1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="AH1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="2">
@@ -708,13 +711,13 @@
         <v>20</v>
       </c>
       <c r="AB2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AC2" t="s">
         <v>17</v>
       </c>
       <c r="AD2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="AE2" t="s">
         <v>17</v>
@@ -923,10 +926,10 @@
         <v>3</v>
       </c>
       <c r="AB4" t="s">
+        <v>29</v>
+      </c>
+      <c r="AC4" t="s">
         <v>28</v>
-      </c>
-      <c r="AC4" t="s">
-        <v>27</v>
       </c>
       <c r="AD4" t="s">
         <v>17</v>
@@ -1222,13 +1225,13 @@
         <v>21</v>
       </c>
       <c r="AB7" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AC7" t="s">
         <v>17</v>
       </c>
       <c r="AD7" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="AE7" t="s">
         <v>17</v>
@@ -1325,7 +1328,7 @@
         <v>7</v>
       </c>
       <c r="AB8" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AC8" t="s">
         <v>17</v>
@@ -1424,7 +1427,7 @@
         <v>22</v>
       </c>
       <c r="AB9" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AC9" t="s">
         <v>17</v>
@@ -1523,7 +1526,7 @@
         <v>23</v>
       </c>
       <c r="AB10" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AC10" t="s">
         <v>17</v>
@@ -1679,7 +1682,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Outcome</t>
+          <t>Outcome at discharge</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1726,10 +1729,10 @@
         <v>1</v>
       </c>
       <c r="AA12" t="s">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="AB12" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AC12" t="s">
         <v>17</v>
@@ -1744,7 +1747,7 @@
         <v>17</v>
       </c>
       <c r="AG12" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="AH12" t="b">
         <v>1</v>
@@ -1825,7 +1828,7 @@
         <v>1</v>
       </c>
       <c r="AA13" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AB13" t="s">
         <v>17</v>
@@ -2023,10 +2026,10 @@
         <v>0</v>
       </c>
       <c r="AA15" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AB15" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AC15" t="s">
         <v>17</v>
@@ -2041,7 +2044,7 @@
         <v>17</v>
       </c>
       <c r="AG15" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="AH15" t="b">
         <v>1</v>
@@ -2227,6 +2230,174 @@
         <v>17</v>
       </c>
       <c r="AH17" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Zimbabwe</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>ZIM_maternal_outcomes</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>mat_age_years_combined</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Maternal age (years) -- canonical (derived)</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>derived</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>numeric</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>Derived (computed by cleaning pipeline Module 15)</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>mat_age_years_combined</t>
+        </is>
+      </c>
+      <c r="K18" t="b">
+        <v>1</v>
+      </c>
+      <c r="M18" t="b">
+        <v>0</v>
+      </c>
+      <c r="P18" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>60</v>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>Derived canonical maternal age in years. Cleaning pipeline Module 15 computes coalesce(matageyrs, mat_age_date_years). ZIM captures matageyrs only (matagedate is a Malawi maternity-form field), so in ZIM data this column always equals matageyrs and mat_age_source is always 'matageyrs'; the shared derivation keeps the two countries on one schema. Emitted only where a source column is present. Originals retained. Not a raw field; no .value column.</t>
+        </is>
+      </c>
+      <c r="W18"/>
+      <c r="X18"/>
+      <c r="Y18"/>
+      <c r="Z18"/>
+      <c r="AA18" t="s">
+        <v>17</v>
+      </c>
+      <c r="AB18" t="s">
+        <v>17</v>
+      </c>
+      <c r="AC18" t="s">
+        <v>17</v>
+      </c>
+      <c r="AD18" t="s">
+        <v>17</v>
+      </c>
+      <c r="AE18" t="s">
+        <v>17</v>
+      </c>
+      <c r="AF18" t="s">
+        <v>17</v>
+      </c>
+      <c r="AG18" t="s">
+        <v>17</v>
+      </c>
+      <c r="AH18" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Zimbabwe</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>ZIM_maternal_outcomes</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>mat_age_source</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Maternal age -- source of the derived value (provenance)</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>derived</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>categorical</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>Derived (computed by cleaning pipeline Module 15)</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>mat_age_source</t>
+        </is>
+      </c>
+      <c r="K19" t="b">
+        <v>1</v>
+      </c>
+      <c r="M19" t="b">
+        <v>0</v>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>Provenance label for mat_age_years_combined, emitted alongside it by Module 15. In ZIM data this is 'matageyrs' wherever an age is present and 'none' otherwise, because matagedate is a Malawi maternity-form field; the 'matagedate_derived' level exists for schema parity with MWI. Not a raw field; no .value column.</t>
+        </is>
+      </c>
+      <c r="W19"/>
+      <c r="X19"/>
+      <c r="Y19"/>
+      <c r="Z19"/>
+      <c r="AA19" t="s">
+        <v>17</v>
+      </c>
+      <c r="AB19" t="s">
+        <v>17</v>
+      </c>
+      <c r="AC19" t="s">
+        <v>17</v>
+      </c>
+      <c r="AD19" t="s">
+        <v>17</v>
+      </c>
+      <c r="AE19" t="s">
+        <v>17</v>
+      </c>
+      <c r="AF19" t="s">
+        <v>17</v>
+      </c>
+      <c r="AG19" t="s">
+        <v>17</v>
+      </c>
+      <c r="AH19" t="b">
         <v>0</v>
       </c>
     </row>
@@ -3126,7 +3297,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Died During Admission</t>
+          <t>Died during admission</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -3216,7 +3387,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Transferred to other Hospital</t>
+          <t>Transferred to other hospital</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -3246,7 +3417,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Discharged on Request</t>
+          <t>Discharged on request</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -4841,6 +5012,64 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Zimbabwe</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>ZIM_maternal_outcomes</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>mat_age_source</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Maternal age -- source of the derived value (provenance)</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>derived</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>categorical</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Derived (computed by cleaning pipeline Module 15)</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>mat_age_source</t>
+        </is>
+      </c>
+      <c r="K2" t="b">
+        <v>1</v>
+      </c>
+      <c r="M2" t="b">
+        <v>0</v>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>Provenance label for mat_age_years_combined, emitted alongside it by Module 15. In ZIM data this is 'matageyrs' wherever an age is present and 'none' otherwise, because matagedate is a Malawi maternity-form field; the 'matagedate_derived' level exists for schema parity with MWI. Not a raw field; no .value column.</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>Categorical with no value map entries</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
